--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/06_infrastructure_platforms.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/06_infrastructure_platforms.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rea829a87971647c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R251ba3c86da14b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R7ae51d1240984d76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R70828be1714740a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rcfeebfb75e254da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rad55f902423943da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMDB Mapping" sheetId="7" r:id="R97558aa1020542d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R2826d603146c42ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R64f90410134047a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcf7dbd9359324418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rd91768f93ac1408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rc177b99800094223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Re5592373b4414f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMDB Mapping" sheetId="7" r:id="R96b3a7b9798a40bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -642,7 +642,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488799f38d4b4182"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6bf2658e8624de5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -833,7 +833,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P6" s="78" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Executive Office Primary Midwest Data Center Hosting Segment (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -886,7 +886,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P7" s="79" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Executive Office AWS Target Landing Zone (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -939,7 +939,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Provider Operations Primary Midwest Data Center Hosting Segment (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q8" t="str">
         <x:v>High</x:v>
@@ -992,7 +992,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Provider Operations AWS Target Landing Zone (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q9" t="str">
         <x:v>Medium</x:v>
@@ -1045,7 +1045,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations Primary Midwest Data Center Hosting Segment (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q10" t="str">
         <x:v>High</x:v>
@@ -1098,7 +1098,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Claims Operations AWS Target Landing Zone (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q11" t="str">
         <x:v>Medium</x:v>
@@ -1151,7 +1151,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Eligibility and Benefits Primary Midwest Data Center Hosting Segment (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q12" t="str">
         <x:v>High</x:v>
@@ -1204,7 +1204,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits AWS Target Landing Zone (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q13" t="str">
         <x:v>Medium</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Prior Authorization and UM Primary Midwest Data Center Hosting Segment (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q14" t="str">
         <x:v>High</x:v>
@@ -1310,7 +1310,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM AWS Target Landing Zone (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q15" t="str">
         <x:v>Medium</x:v>
@@ -1363,7 +1363,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Contact Center and Member Service Primary Midwest Data Center Hosting Segment (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q16" t="str">
         <x:v>Medium</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Contact Center and Member Service AWS Target Landing Zone (record 12) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q17" t="str">
         <x:v>Medium</x:v>
@@ -1469,7 +1469,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations Primary Midwest Data Center Hosting Segment (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q18" t="str">
         <x:v>High</x:v>
@@ -1522,7 +1522,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations AWS Target Landing Zone (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q19" t="str">
         <x:v>Medium</x:v>
@@ -1575,7 +1575,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Finance Analytics Primary Midwest Data Center Hosting Segment (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q20" t="str">
         <x:v>High</x:v>
@@ -1628,7 +1628,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Finance Analytics AWS Target Landing Zone (record 16) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q21" t="str">
         <x:v>Medium</x:v>
@@ -1681,7 +1681,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Workforce Analytics Primary Midwest Data Center Hosting Segment (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q22" t="str">
         <x:v>High</x:v>
@@ -1734,7 +1734,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics AWS Target Landing Zone (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q23" t="str">
         <x:v>Medium</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics Primary Midwest Data Center Hosting Segment (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q24" t="str">
         <x:v>High</x:v>
@@ -1840,7 +1840,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics AWS Target Landing Zone (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q25" t="str">
         <x:v>Medium</x:v>
@@ -1893,7 +1893,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Claims and Payment Analytics Primary Midwest Data Center Hosting Segment (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q26" t="str">
         <x:v>Medium</x:v>
@@ -1946,7 +1946,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Claims and Payment Analytics AWS Target Landing Zone (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q27" t="str">
         <x:v>Medium</x:v>
@@ -1999,7 +1999,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics Primary Midwest Data Center Hosting Segment (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q28" t="str">
         <x:v>High</x:v>
@@ -2052,7 +2052,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Provider Performance Analytics AWS Target Landing Zone (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q29" t="str">
         <x:v>Medium</x:v>
@@ -2105,7 +2105,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform Primary Midwest Data Center Hosting Segment (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q30" t="str">
         <x:v>High</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Enterprise Data Platform AWS Target Landing Zone (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q31" t="str">
         <x:v>Medium</x:v>
@@ -2211,7 +2211,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Data Governance and Data Quality Primary Midwest Data Center Hosting Segment (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q32" t="str">
         <x:v>High</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality AWS Target Landing Zone (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q33" t="str">
         <x:v>Medium</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Primary Midwest Data Center Hosting Segment (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q34" t="str">
         <x:v>High</x:v>
@@ -2370,7 +2370,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action AWS Target Landing Zone (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q35" t="str">
         <x:v>Medium</x:v>
@@ -2423,7 +2423,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse Primary Midwest Data Center Hosting Segment (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q36" t="str">
         <x:v>Medium</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Unified Clinical and Claims Lakehouse AWS Target Landing Zone (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q37" t="str">
         <x:v>Medium</x:v>
@@ -2529,7 +2529,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Primary Midwest Data Center Hosting Segment (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>High</x:v>
@@ -2582,7 +2582,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline AWS Target Landing Zone (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Medium</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Primary Midwest Data Center Hosting Segment (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>High</x:v>
@@ -2688,7 +2688,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Vendor and Contract Optimization AWS Target Landing Zone (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Medium</x:v>
@@ -2741,7 +2741,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Infrastructure and CMDB Primary Midwest Data Center Hosting Segment (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>High</x:v>
@@ -2794,7 +2794,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Infrastructure and CMDB AWS Target Landing Zone (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Medium</x:v>
@@ -2847,7 +2847,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations Primary Midwest Data Center Hosting Segment (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>High</x:v>
@@ -2900,7 +2900,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations AWS Target Landing Zone (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Medium</x:v>
@@ -2927,7 +2927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6beaee604eaa4983"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdff3a115e6ef4155"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3002,7 +3002,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f6da5d04ac04059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0f6ce1cf4e44c14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3206,7 +3206,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1c917ef369c411f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re190f5688892430d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3284,7 +3284,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d9ffe050ebd4a66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52385dcb75ba4bac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3394,7 +3394,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d17d51639f44034"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b41cba93576445b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3502,7 +3502,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2172ebc0bab4501"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf53053b5e7ae4795"/>
   </x:tableParts>
 </x:worksheet>
 </file>